--- a/output/pdf_financials_xlsx/TNGD.xlsx
+++ b/output/pdf_financials_xlsx/TNGD.xlsx
@@ -2135,15 +2135,11 @@
           <t>Cash Flow from Financing</t>
         </is>
       </c>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B129" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C129" s="3" t="n">
+        <v>28.099</v>
       </c>
     </row>
     <row r="130">
@@ -2217,15 +2213,11 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>-2.08</v>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>0.922</v>
       </c>
     </row>
   </sheetData>
@@ -2938,7 +2930,11 @@
           <t>Net cash (used in)/generated from operating activities</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="n">
         <v>-2.08</v>
       </c>
